--- a/Outputs/Scenarios/PtX_demand_PL_Ammonia.xlsx
+++ b/Outputs/Scenarios/PtX_demand_PL_Ammonia.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.01032955500440896</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00310974915208654</v>
+        <v>0.003376484447995585</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.0006989346058959548</v>
       </c>
     </row>
     <row r="18">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00621949830417308</v>
+        <v>0.005591476847167639</v>
       </c>
     </row>
     <row r="20">
@@ -1481,7 +1481,7 @@
         <v>0.0001488314026094087</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001036583050695514</v>
+        <v>0.0006989346058959548</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.01529164859790063</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01678264658449233</v>
+        <v>0.01822215954322981</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.003771999573841128</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.03356529316898466</v>
+        <v>0.03017599659072902</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.000804823610415823</v>
       </c>
       <c r="K42" t="n">
-        <v>0.00559421552816411</v>
+        <v>0.003771999573841128</v>
       </c>
     </row>
     <row r="43">
